--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_basbrut_a_2019_los_lagos.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_basbrut_a_2019_los_lagos.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:00</t>
+    <t xml:space="preserve">2026-09-24 00:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -684,7 +684,7 @@
         <v>0.3</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0.03</v>
@@ -704,10 +704,10 @@
         <v>30</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>-0.36</v>
@@ -730,7 +730,7 @@
         <v>0.25</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0.2</v>
@@ -744,16 +744,16 @@
         <v>16</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0.33</v>
@@ -799,7 +799,7 @@
         <v>-0.14</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>-0.23</v>
@@ -819,13 +819,13 @@
         <v>30</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.26</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="15">
@@ -845,7 +845,7 @@
         <v>0.03</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>-0.06</v>
